--- a/artfynd/A 23061-2026 artfynd.xlsx
+++ b/artfynd/A 23061-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68154038</v>
+        <v>68154037</v>
       </c>
       <c r="B2" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589785.0702423924</v>
+        <v>589790</v>
       </c>
       <c r="R2" t="n">
-        <v>6468544.229754621</v>
+        <v>6468531</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68154037</v>
+        <v>131617246</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589790.1009124351</v>
+        <v>589704</v>
       </c>
       <c r="R3" t="n">
-        <v>6468531.218636595</v>
+        <v>6468577</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68154035</v>
+        <v>131617245</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589806.8024943346</v>
+        <v>589803</v>
       </c>
       <c r="R4" t="n">
-        <v>6468606.15340984</v>
+        <v>6468547</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68154036</v>
+        <v>68154035</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589782.9075018858</v>
+        <v>589807</v>
       </c>
       <c r="R5" t="n">
-        <v>6468546.8056078</v>
+        <v>6468606</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,28 +1034,17 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68154034</v>
+        <v>131617244</v>
       </c>
       <c r="B6" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589817.0297706106</v>
+        <v>589859</v>
       </c>
       <c r="R6" t="n">
-        <v>6468618.987163948</v>
+        <v>6468622</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,12 +1148,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1239,7 +1163,7 @@
         <v>131617251</v>
       </c>
       <c r="B7" t="n">
-        <v>96680</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131617250</v>
+        <v>68154038</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,45 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589674</v>
+        <v>589785</v>
       </c>
       <c r="R8" t="n">
-        <v>6468598</v>
+        <v>6468544</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,60 +1342,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131617245</v>
+        <v>68154036</v>
       </c>
       <c r="B9" t="n">
-        <v>96573</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589803</v>
+        <v>589783</v>
       </c>
       <c r="R9" t="n">
         <v>6468547</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1503,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,28 +1433,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131617246</v>
+        <v>68154039</v>
       </c>
       <c r="B10" t="n">
-        <v>78976</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,37 +1463,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589704</v>
+        <v>589778</v>
       </c>
       <c r="R10" t="n">
-        <v>6468577</v>
+        <v>6468529</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,12 +1517,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,15 +1537,411 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131617249</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589721</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6468563</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131617250</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589674</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6468598</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131617233</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589859</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6468614</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>68154034</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589817</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6468619</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23061-2026 artfynd.xlsx
+++ b/artfynd/A 23061-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131617245</v>
+        <v>134586956</v>
       </c>
       <c r="B4" t="n">
-        <v>96676</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Brända mossen, Brända mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589803</v>
+        <v>589757</v>
       </c>
       <c r="R4" t="n">
-        <v>6468547</v>
+        <v>6468544</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +934,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sparsam, men mkt fin gammal tallåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,22 +959,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68154035</v>
+        <v>131617245</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>96676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +982,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589807</v>
+        <v>589803</v>
       </c>
       <c r="R5" t="n">
-        <v>6468606</v>
+        <v>6468547</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,22 +1056,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131617244</v>
+        <v>68154035</v>
       </c>
       <c r="B6" t="n">
-        <v>96783</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,17 +1099,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589859</v>
+        <v>589807</v>
       </c>
       <c r="R6" t="n">
-        <v>6468622</v>
+        <v>6468606</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,19 +1153,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131617251</v>
+        <v>131617244</v>
       </c>
       <c r="B7" t="n">
         <v>96783</v>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589634</v>
+        <v>589859</v>
       </c>
       <c r="R7" t="n">
-        <v>6468615</v>
+        <v>6468622</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68154038</v>
+        <v>131617251</v>
       </c>
       <c r="B8" t="n">
-        <v>92333</v>
+        <v>96783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1273,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589785</v>
+        <v>589634</v>
       </c>
       <c r="R8" t="n">
-        <v>6468544</v>
+        <v>6468615</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1322,12 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1342,44 +1347,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68154036</v>
+        <v>68154038</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589783</v>
+        <v>589785</v>
       </c>
       <c r="R9" t="n">
-        <v>6468547</v>
+        <v>6468544</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1433,7 +1438,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1452,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68154039</v>
+        <v>68154036</v>
       </c>
       <c r="B10" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589778</v>
+        <v>589783</v>
       </c>
       <c r="R10" t="n">
-        <v>6468529</v>
+        <v>6468547</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1531,6 +1535,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1549,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131617249</v>
+        <v>68154039</v>
       </c>
       <c r="B11" t="n">
-        <v>79992</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,37 +1565,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589721</v>
+        <v>589778</v>
       </c>
       <c r="R11" t="n">
-        <v>6468563</v>
+        <v>6468529</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1614,12 +1619,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1634,65 +1639,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131617250</v>
+        <v>131617249</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589674</v>
+        <v>589721</v>
       </c>
       <c r="R12" t="n">
-        <v>6468598</v>
+        <v>6468563</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1751,10 +1748,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131617233</v>
+        <v>131617250</v>
       </c>
       <c r="B13" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,34 +1759,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589859</v>
+        <v>589674</v>
       </c>
       <c r="R13" t="n">
-        <v>6468614</v>
+        <v>6468598</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1848,10 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68154034</v>
+        <v>131617233</v>
       </c>
       <c r="B14" t="n">
-        <v>106244</v>
+        <v>8460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,37 +1864,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589817</v>
+        <v>589859</v>
       </c>
       <c r="R14" t="n">
-        <v>6468619</v>
+        <v>6468614</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1913,12 +1918,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1933,15 +1938,218 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134588290</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyborg, Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589946</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6468850</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>68154034</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589817</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6468619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23061-2026 artfynd.xlsx
+++ b/artfynd/A 23061-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131617245</v>
+        <v>134636789</v>
       </c>
       <c r="B5" t="n">
-        <v>96676</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589803</v>
+        <v>589845</v>
       </c>
       <c r="R5" t="n">
-        <v>6468547</v>
+        <v>6468820</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68154035</v>
+        <v>131617245</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>96676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,37 +1079,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589807</v>
+        <v>589803</v>
       </c>
       <c r="R6" t="n">
-        <v>6468606</v>
+        <v>6468547</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1153,22 +1153,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131617244</v>
+        <v>68154035</v>
       </c>
       <c r="B7" t="n">
-        <v>96783</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589859</v>
+        <v>589807</v>
       </c>
       <c r="R7" t="n">
-        <v>6468622</v>
+        <v>6468606</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,19 +1250,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131617251</v>
+        <v>131617244</v>
       </c>
       <c r="B8" t="n">
         <v>96783</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589634</v>
+        <v>589859</v>
       </c>
       <c r="R8" t="n">
-        <v>6468615</v>
+        <v>6468622</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68154038</v>
+        <v>131617251</v>
       </c>
       <c r="B9" t="n">
-        <v>92333</v>
+        <v>96783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589785</v>
+        <v>589634</v>
       </c>
       <c r="R9" t="n">
-        <v>6468544</v>
+        <v>6468615</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1444,60 +1444,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68154036</v>
+        <v>134636791</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>96783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589783</v>
+        <v>589825</v>
       </c>
       <c r="R10" t="n">
-        <v>6468547</v>
+        <v>6468816</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1535,67 +1535,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68154039</v>
+        <v>134636793</v>
       </c>
       <c r="B11" t="n">
-        <v>93235</v>
+        <v>96783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589778</v>
+        <v>589848</v>
       </c>
       <c r="R11" t="n">
-        <v>6468529</v>
+        <v>6468840</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1619,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1639,44 +1638,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131617249</v>
+        <v>134636796</v>
       </c>
       <c r="B12" t="n">
-        <v>79992</v>
+        <v>96783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589721</v>
+        <v>589884</v>
       </c>
       <c r="R12" t="n">
-        <v>6468563</v>
+        <v>6468769</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1716,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1748,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131617250</v>
+        <v>134636801</v>
       </c>
       <c r="B13" t="n">
-        <v>57162</v>
+        <v>96783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,42 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589674</v>
+        <v>589839</v>
       </c>
       <c r="R13" t="n">
-        <v>6468598</v>
+        <v>6468650</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1821,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1853,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131617233</v>
+        <v>68154038</v>
       </c>
       <c r="B14" t="n">
-        <v>8460</v>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1864,37 +1855,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fredrikslund, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589859</v>
+        <v>589785</v>
       </c>
       <c r="R14" t="n">
-        <v>6468614</v>
+        <v>6468544</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1918,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,69 +1929,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134588290</v>
+        <v>68154036</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyborg, Nyborg, Ög</t>
+          <t>Hösterum, Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589946</v>
+        <v>589783</v>
       </c>
       <c r="R15" t="n">
-        <v>6468850</v>
+        <v>6468547</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2024,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,50 +2020,51 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68154034</v>
+        <v>68154039</v>
       </c>
       <c r="B16" t="n">
-        <v>106244</v>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589817</v>
+        <v>589778</v>
       </c>
       <c r="R16" t="n">
-        <v>6468619</v>
+        <v>6468529</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2150,6 +2133,904 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131617249</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589721</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6468563</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134636792</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589838</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6468838</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134636794</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>589862</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6468806</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134636795</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>589884</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6468769</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131617250</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>589674</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6468598</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134636790</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>589838</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6468815</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131617233</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>589859</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6468614</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134588290</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nyborg, Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>589946</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6468850</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>68154034</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>589817</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6468619</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23061-2026 artfynd.xlsx
+++ b/artfynd/A 23061-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617251</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154037</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617246</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134586956</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636789</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617245</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154035</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617244</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636791</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636793</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636796</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636801</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154038</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2036,6 +2106,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154036</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2133,6 +2208,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154039</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2230,6 +2310,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617249</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2327,6 +2412,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636792</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2424,6 +2514,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636794</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2521,6 +2616,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636795</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617250</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2731,6 +2836,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636790</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617233</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2934,6 +3049,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134588290</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3031,8 +3151,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>